--- a/04_Маршрутные_карты/Детали/МК_PSH24-052.01-01.xlsx
+++ b/04_Маршрутные_карты/Детали/МК_PSH24-052.01-01.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Деталь 764×455×105</t>
+          <t>Панель гнутая, s=5,9</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Деталь 764×455×105</t>
+          <t>Панель гнутая, s=5,9</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -607,30 +607,30 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Заготовка по чертежу (резка/литая/сварная заготовка), комплектование</t>
+          <t>Раскрой листа s=5.9 по DXF (заготовка с припуском на гибы)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Ленточнопильный станок (Pilous ARG 300 / Контур-302) / участок заготовок</t>
+          <t>Станок лазерной резки (LVD Phoenix 3015 / LS-3015), 3 кВт</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>По технологу</t>
+          <t>Стол раскройный</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Припуск на механическую обработку по технологу</t>
+          <t>Допуск реза ±0,5 мм</t>
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Входной контроль</t>
+          <t>Визуальный, замер</t>
         </is>
       </c>
     </row>
@@ -642,35 +642,35 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Механическая</t>
+          <t>Гибочная</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Механическая обработка по чертежу (токарно-фрезерная)</t>
+          <t>Гибка на листогибочном прессе по чертежу (линии гиба — по разметке/чертилке)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Токарно-винторезный станок 16К20 / Doosan Puma 2600 / Фрезерный обрабатывающий центр (Haas VF-2 / 6Р13)</t>
+          <t>Листогибочный пресс (Gasparini PBS 135/3100, ЧПУ)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Универсальная оснастка</t>
+          <t>Пуансоны/матрицы по углу гиба, упоры</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Допуски по ГОСТ 25058-2016; Ra 6,3..12,5</t>
+          <t>Угол по чертежу ±0,5°; радиус гиба по чертежу; контролировать прогиб</t>
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.66</v>
+        <v>0.27</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Контроль по чертежу</t>
+          <t>Угольник, шаблон</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Снятие заусенцев, зачистка</t>
+          <t>Снятие заусенцев, правка, зачистка</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Кромки R0,5</t>
+          <t>Недопустимы трещины на линии гиба</t>
         </is>
       </c>
       <c r="G9" s="6" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1.03</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="13">
